--- a/artfynd/A 38982-2024 artfynd.xlsx
+++ b/artfynd/A 38982-2024 artfynd.xlsx
@@ -3876,7 +3876,7 @@
         <v>120482257</v>
       </c>
       <c r="B30" t="n">
-        <v>5179</v>
+        <v>5182</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 38982-2024 artfynd.xlsx
+++ b/artfynd/A 38982-2024 artfynd.xlsx
@@ -3876,7 +3876,7 @@
         <v>120482257</v>
       </c>
       <c r="B30" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
